--- a/Verlog.xlsx
+++ b/Verlog.xlsx
@@ -1,40 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" mc:Ignorable="x15ac">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="F:\MABd2v26.09.5\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
+  <x15ac:absPath url="F:\MABd2v26.09.5\"/>
   <bookViews>
-    <workbookView windowWidth="29415" windowHeight="15015"/>
+    <workbookView activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId3"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId4"/>
+    <sheet name="Sheet3" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+  <si>
+    <t/>
+  </si>
   <si>
     <t>更新说明：</t>
   </si>
@@ -220,179 +205,266 @@
   </si>
   <si>
     <t>3.因本项目目前并没有接入Mirror酱，故封闭了软件内自带的mirror酱填写入口，请勿购买CDKEY，使用BAT启动器即可自动更新</t>
+  </si>
+  <si>
+    <t>v26.09.11（20260923）</t>
+  </si>
+  <si>
+    <t>1.狩猎场增加了自动刷取最少圣石的新功能</t>
+  </si>
+  <si>
+    <t>2.合并了日常收菜一条龙和日常奖励一条龙</t>
+  </si>
+  <si>
+    <t>3.增加了更多卡带的收集召集任务</t>
+  </si>
+  <si>
+    <t>4.增加了跑商一键购买任务</t>
+  </si>
+  <si>
+    <t>5.魔兽回归赛季自动战斗</t>
+  </si>
+  <si>
+    <t>v26.09.11（20260924）</t>
+  </si>
+  <si>
+    <t>1.狩猎场新增“自动：刷数量最少的圣石”：自动读取资源栏五种圣石的数量，刷当前最少的一种，长期各属性自然均衡；读不到数量时会弹提示并中止该任务；</t>
+  </si>
+  <si>
+    <t>2.任务整合：“领取公会低保”“经营管理”“广场女神像奖励”三个任务合并为“日常收菜”；“每日任务奖励”“活动奖励”两个任务合并为“奖励一键领取”，任务列表更精简；</t>
+  </si>
+  <si>
+    <t>3.资源吸收和召集拆分为“首轮/次轮”两个独立任务，各自可勾选执行周期；并新增更多卡带的收集与召集；</t>
+  </si>
+  <si>
+    <t>4.赛季活动商店新增“跑商一键购买”：购买内容与执行周期自选；</t>
+  </si>
+  <si>
+    <t>5.新增“回归赛季魔兽快速战斗”任务；</t>
+  </si>
+  <si>
+    <t>6.装备分解+精炼新增19分/20分档位（原来只能精炼18分装备）；</t>
+  </si>
+  <si>
+    <t>7.重构活动奖励领取流程：废弃“小红点”图片模板检测（红点样式一变就失效），改为绿色遮罩模板+任务/兑换所/转盘/骰子四类活动统一分支，修掉进入活动页就卡死的问题；</t>
+  </si>
+  <si>
+    <t>8.修复救赎之塔“MAX”次数识别与镜中之战PVP网络卡顿时无法进入战斗的问题，并补上救赎之塔赛季事件、魔兽赛季的奖励领取；</t>
+  </si>
+  <si>
+    <t>9.正式接入Mirror酱：MXU“设置→更新”的内置更新入口已开放（认准资源ID Maa-Assistant-Browndust2；不购买CDK也可用BAT启动器照常更新）；</t>
+  </si>
+  <si>
+    <t>10.启动器新增-Repair修复安装，并会在启动时自动清理旧版本遗留的说明文档/教学视频/已下架的任务文件，升级后目录里只留当前版本那一份；</t>
+  </si>
+  <si>
+    <t>11.注意事项文档改为.docx随包派发；</t>
+  </si>
+  <si>
+    <t>12.游戏分辨率不符合要求时弹窗告警并停止任务，任务失败时给出反馈入口提示。</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="6">
+    <numFmt numFmtId="300" formatCode="General"/>
+    <numFmt numFmtId="301" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="302" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="303" formatCode="0%"/>
+    <numFmt numFmtId="304" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="305" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
-    <font>
-      <sz val="11"/>
+  <fonts count="25">
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="等线"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
+      <color rgb="FF175CEB"/>
+      <sz val="10"/>
+      <u/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Segoe UI Symbol"/>
+      <family val="2"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
       <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF000000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
       <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
       <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFF0000"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
       <color theme="3"/>
+      <sz val="15"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF3F3F76"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FFFA7D00"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
+      <b val="1"/>
       <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="0"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <name val="宋体"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -400,6 +472,9 @@
       <patternFill patternType="gray125"/>
     </fill>
     <fill>
+      <patternFill patternType="none"/>
+    </fill>
+    <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
@@ -449,19 +524,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -473,19 +548,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -497,19 +572,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -521,19 +596,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -545,19 +620,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -569,24 +644,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.799982"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599994"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399976"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="10">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -623,7 +705,7 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4" tint="0.499985"/>
       </bottom>
       <diagonal/>
     </border>
@@ -693,171 +775,192 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="49">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0">
+  <cellStyleXfs>
+    <xf numFmtId="300" fontId="5" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="6" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="301" fontId="5" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="302" fontId="5" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="303" fontId="5" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="304" fontId="5" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="305" fontId="5" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="7" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="5" fillId="3" borderId="2" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="8" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="9" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="10" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="11" fillId="2" borderId="3" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="12" fillId="2" borderId="3" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="2" borderId="4" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="13" fillId="2" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="14" fillId="4" borderId="5" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="15" fillId="5" borderId="6" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="16" fillId="5" borderId="5" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="17" fillId="6" borderId="7" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="18" fillId="2" borderId="8" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="19" fillId="2" borderId="9" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="20" fillId="7" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="21" fillId="8" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="22" fillId="9" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="10" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="11" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="12" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="13" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="14" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="15" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="16" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="17" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="18" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="19" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="20" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="21" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="22" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="23" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="24" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="25" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="26" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="27" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="28" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="29" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="30" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="31" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="24" fillId="32" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="23" fillId="33" borderId="1" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+  <cellXfs count="9">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="5" fillId="0" borderId="1" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles>
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
+    <cellStyle name="千位分隔" xfId="2" builtinId="3"/>
+    <cellStyle name="货币" xfId="3" builtinId="4"/>
+    <cellStyle name="百分比" xfId="4" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="5" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="6" builtinId="7"/>
     <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
     <cellStyle name="注释" xfId="8" builtinId="10"/>
     <cellStyle name="警告文本" xfId="9" builtinId="11"/>
@@ -901,12 +1004,6 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
 </styleSheet>
 </file>
 
@@ -1158,322 +1255,387 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A1:A82"/>
+  <dimension ref="A96"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="171.125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>0</v>
+      <c r="A1" s="4" t="s">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:1">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
+      <c r="A3" s="5" t="s">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:1">
-      <c r="A4" t="s">
-        <v>2</v>
+      <c r="A4" s="4" t="s">
+        <v>3</v>
       </c>
     </row>
     <row r="7" spans="1:1">
-      <c r="A7" s="1" t="s">
-        <v>3</v>
+      <c r="A7" s="5" t="s">
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:1">
-      <c r="A8" t="s">
-        <v>4</v>
+      <c r="A8" s="4" t="s">
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:1">
-      <c r="A11" s="1" t="s">
-        <v>5</v>
+      <c r="A11" s="5" t="s">
+        <v>6</v>
       </c>
     </row>
     <row r="12" spans="1:1">
-      <c r="A12" t="s">
-        <v>6</v>
+      <c r="A12" s="4" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:1">
-      <c r="A13" t="s">
-        <v>7</v>
+      <c r="A13" s="4" t="s">
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:1">
-      <c r="A14" t="s">
-        <v>8</v>
+      <c r="A14" s="4" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>9</v>
+      <c r="A15" s="4" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="17" spans="1:1">
-      <c r="A17" s="1" t="s">
-        <v>10</v>
+      <c r="A17" s="5" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:1">
-      <c r="A18" t="s">
-        <v>11</v>
+      <c r="A18" s="4" t="s">
+        <v>12</v>
       </c>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="1" t="s">
-        <v>12</v>
+      <c r="A20" s="5" t="s">
+        <v>13</v>
       </c>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" t="s">
-        <v>13</v>
+      <c r="A21" s="4" t="s">
+        <v>14</v>
       </c>
     </row>
     <row r="22" spans="1:1">
-      <c r="A22" t="s">
-        <v>14</v>
+      <c r="A22" s="4" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="24" spans="1:1">
-      <c r="A24" s="1" t="s">
-        <v>15</v>
+      <c r="A24" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="25" spans="1:1">
-      <c r="A25" t="s">
-        <v>16</v>
+      <c r="A25" s="4" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="26" spans="1:1">
-      <c r="A26" t="s">
-        <v>17</v>
+      <c r="A26" s="4" t="s">
+        <v>18</v>
       </c>
     </row>
     <row r="28" spans="1:1">
-      <c r="A28" s="1" t="s">
-        <v>18</v>
+      <c r="A28" s="5" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="29" spans="1:1">
-      <c r="A29" t="s">
-        <v>19</v>
+      <c r="A29" s="4" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="31" spans="1:1">
-      <c r="A31" s="1" t="s">
-        <v>20</v>
+      <c r="A31" s="5" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="1:1">
-      <c r="A32" t="s">
-        <v>21</v>
+      <c r="A32" s="4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="1:1">
-      <c r="A33" t="s">
-        <v>22</v>
+      <c r="A33" s="4" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="35" spans="1:1">
-      <c r="A35" s="1" t="s">
-        <v>23</v>
+      <c r="A35" s="5" t="s">
+        <v>24</v>
       </c>
     </row>
     <row r="36" spans="1:1">
-      <c r="A36" t="s">
-        <v>24</v>
+      <c r="A36" s="4" t="s">
+        <v>25</v>
       </c>
     </row>
     <row r="38" spans="1:1">
-      <c r="A38" s="1" t="s">
-        <v>25</v>
+      <c r="A38" s="5" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="39" spans="1:1">
-      <c r="A39" t="s">
-        <v>26</v>
+      <c r="A39" s="4" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="40" spans="1:1">
-      <c r="A40" t="s">
-        <v>27</v>
+      <c r="A40" s="4" t="s">
+        <v>28</v>
       </c>
     </row>
     <row r="42" spans="1:1">
-      <c r="A42" s="1" t="s">
-        <v>28</v>
+      <c r="A42" s="5" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="43" spans="1:1">
-      <c r="A43" t="s">
-        <v>29</v>
+      <c r="A43" s="4" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="44" spans="1:1">
-      <c r="A44" t="s">
-        <v>30</v>
+      <c r="A44" s="4" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:1">
-      <c r="A45" t="s">
-        <v>31</v>
+      <c r="A45" s="4" t="s">
+        <v>32</v>
       </c>
     </row>
     <row r="46" spans="1:1">
-      <c r="A46" t="s">
-        <v>32</v>
+      <c r="A46" s="4" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="48" spans="1:1">
-      <c r="A48" s="1" t="s">
-        <v>33</v>
+      <c r="A48" s="5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" t="s">
-        <v>34</v>
+      <c r="A49" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" t="s">
-        <v>35</v>
+      <c r="A50" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" t="s">
-        <v>36</v>
+      <c r="A51" s="4" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="52" spans="1:1">
-      <c r="A52" t="s">
-        <v>37</v>
+      <c r="A52" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="53" spans="1:1">
-      <c r="A53" t="s">
-        <v>38</v>
+      <c r="A53" s="4" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="55" spans="1:1">
-      <c r="A55" s="1" t="s">
-        <v>39</v>
+      <c r="A55" s="5" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="56" spans="1:1">
-      <c r="A56" t="s">
-        <v>40</v>
+      <c r="A56" s="4" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="57" spans="1:1">
-      <c r="A57" t="s">
-        <v>41</v>
+      <c r="A57" s="4" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="58" spans="1:1">
-      <c r="A58" t="s">
-        <v>42</v>
+      <c r="A58" s="4" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="59" spans="1:1">
-      <c r="A59" t="s">
-        <v>43</v>
+      <c r="A59" s="4" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="60" spans="1:1">
-      <c r="A60" t="s">
-        <v>44</v>
+      <c r="A60" s="4" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="62" spans="1:1">
-      <c r="A62" s="1" t="s">
-        <v>45</v>
+      <c r="A62" s="5" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="63" spans="1:1">
-      <c r="A63" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="65" s="1" customFormat="1" spans="1:1">
-      <c r="A65" s="1" t="s">
+      <c r="A63" s="4" t="s">
         <v>47</v>
       </c>
     </row>
+    <row r="65" spans="1:1" s="8" customFormat="1">
+      <c r="A65" s="5" t="s">
+        <v>48</v>
+      </c>
+    </row>
     <row r="66" spans="1:1">
-      <c r="A66" t="s">
-        <v>48</v>
+      <c r="A66" s="4" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="68" spans="1:1">
-      <c r="A68" s="1" t="s">
-        <v>49</v>
+      <c r="A68" s="5" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>50</v>
+      <c r="A69" s="4" t="s">
+        <v>51</v>
       </c>
     </row>
     <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="72" s="1" customFormat="1" spans="1:1">
-      <c r="A72" s="1" t="s">
+      <c r="A70" s="4" t="s">
         <v>52</v>
       </c>
     </row>
+    <row r="72" spans="1:1" s="8" customFormat="1">
+      <c r="A72" s="5" t="s">
+        <v>53</v>
+      </c>
+    </row>
     <row r="73" spans="1:1">
-      <c r="A73" t="s">
-        <v>53</v>
+      <c r="A73" s="4" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="74" spans="1:1">
-      <c r="A74" t="s">
-        <v>54</v>
+      <c r="A74" s="4" t="s">
+        <v>55</v>
       </c>
     </row>
     <row r="75" spans="1:1">
-      <c r="A75" t="s">
-        <v>55</v>
+      <c r="A75" s="4" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="76" spans="1:1">
-      <c r="A76" t="s">
-        <v>56</v>
+      <c r="A76" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="77" spans="1:1">
-      <c r="A77" t="s">
-        <v>57</v>
+      <c r="A77" s="4" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="79" spans="1:1">
-      <c r="A79" s="1" t="s">
-        <v>58</v>
+      <c r="A79" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="80" spans="1:1">
-      <c r="A80" t="s">
-        <v>59</v>
+      <c r="A80" s="4" t="s">
+        <v>60</v>
       </c>
     </row>
     <row r="81" spans="1:1">
-      <c r="A81" t="s">
-        <v>60</v>
+      <c r="A81" s="4" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:1">
-      <c r="A82" t="s">
-        <v>61</v>
+      <c r="A82" s="4" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1" s="8" customFormat="1">
+      <c r="A84" s="6" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85" s="7" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86" s="7" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87" s="7" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88" s="7" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89" s="4" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
@@ -1484,7 +1646,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
@@ -1496,7 +1658,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
   <dimension ref="A1"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>

--- a/Verlog.xlsx
+++ b/Verlog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
   <si>
     <t/>
   </si>
@@ -207,24 +207,6 @@
     <t>3.因本项目目前并没有接入Mirror酱，故封闭了软件内自带的mirror酱填写入口，请勿购买CDKEY，使用BAT启动器即可自动更新</t>
   </si>
   <si>
-    <t>v26.09.11（20260923）</t>
-  </si>
-  <si>
-    <t>1.狩猎场增加了自动刷取最少圣石的新功能</t>
-  </si>
-  <si>
-    <t>2.合并了日常收菜一条龙和日常奖励一条龙</t>
-  </si>
-  <si>
-    <t>3.增加了更多卡带的收集召集任务</t>
-  </si>
-  <si>
-    <t>4.增加了跑商一键购买任务</t>
-  </si>
-  <si>
-    <t>5.魔兽回归赛季自动战斗</t>
-  </si>
-  <si>
     <t>v26.09.11（20260924）</t>
   </si>
   <si>
@@ -262,6 +244,48 @@
   </si>
   <si>
     <t>12.游戏分辨率不符合要求时弹窗告警并停止任务，任务失败时给出反馈入口提示。</t>
+  </si>
+  <si>
+    <t>v26.09.12（20260926）</t>
+  </si>
+  <si>
+    <t>1.镜中之战PVP改为从广场直接点入口进入（新增广场入口图片识别），不再依赖地图移动，修掉「走到一半进不去 / 卡在选择卡带界面」的问题；</t>
+  </si>
+  <si>
+    <t>2.镜中之战PVP细节加固：自动战斗按钮限制重复点击次数并补等待时间，卡带与玩法关键词识别放宽，餐厅与营业入口改为固定坐标点击，减少误点与空转；</t>
+  </si>
+  <si>
+    <t>3.奖励一键领取：活动页签由「一个大区域整体识别」拆成四个页签逐个识别并点击，漏领概率大幅降低；</t>
+  </si>
+  <si>
+    <t>4.奖励一键领取：去掉已失效的「活动主页」图片模板节点，改为识别活动标签后直接进入四个页签；</t>
+  </si>
+  <si>
+    <t>5.奖励一键领取：列表滑动检测改为「向下滑 / 向上滑」双向轮询（原来只向下滑且滑完就放弃），并去掉会导致任务报错中断的错误分支，长列表也能翻到位；</t>
+  </si>
+  <si>
+    <t>6.日常收菜：每日与广场奖励节点限制重复命中次数，并去掉末尾的兜底重启节点，避免在识别不到时原地打转；</t>
+  </si>
+  <si>
+    <t>7.回归赛季魔兽快速战斗：进入时增加「回归赛季」关键词识别、连点两次并延长等待，修掉入口点不进去的问题；</t>
+  </si>
+  <si>
+    <t>8.回归赛季魔兽快速战斗：新增「升级提示」的识别与关闭，结算后能自动回到快速战斗循环，不再直接结束任务；</t>
+  </si>
+  <si>
+    <t>9.启动器：更新全程写入 debug/updater.log（版本检测结果、逐一下载源的成功或失败与实际字节数、包身份校验、覆盖失败文件清单、安装前后版本号、最终结论），用户反馈「更新完版本号没变」时可凭日志直接定位；</t>
+  </si>
+  <si>
+    <t>10.启动器：连不上 GitHub 时不再完全静默——日志记下原因，并每 24 小时最多弹一次提示，明确告知「本次没有做任何更新、当前仍是 vX」，附发布页入口；</t>
+  </si>
+  <si>
+    <t>11.启动器：显式开启 TLS 1.2（老机器的 Windows PowerShell 5.1 默认只开 Ssl3 与 Tls，症状是「更新检查毫无动静、版本永远停在旧版」）；</t>
+  </si>
+  <si>
+    <t>12.启动器：主流程未捕获的异常不再静默吞掉，会弹提示并写入日志；顺带修掉一处多段字符串拼接后再格式化的 bug（错误弹窗里的占位符会原样显示）；</t>
+  </si>
+  <si>
+    <t>13.README 与注意事项文档同步更新：常见问题扩充到 Q13，并明确「分辨率只能用固定档位（1280×720 / 1600×900 / 1920×1080 / 2560×1440 / 3840×2160），不要用鼠标拖窗口边框改大小」。</t>
   </si>
 </sst>
 </file>
@@ -924,7 +948,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -948,6 +972,9 @@
     </xf>
     <xf numFmtId="300" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1257,7 +1284,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A96"/>
+  <dimension ref="A111"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="171.125" customWidth="1"/>
@@ -1498,7 +1525,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="1:1" s="8" customFormat="1">
+    <row r="65" spans="1:1" s="9" customFormat="1">
       <c r="A65" s="5" t="s">
         <v>48</v>
       </c>
@@ -1523,7 +1550,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="72" spans="1:1" s="8" customFormat="1">
+    <row r="72" spans="1:1" s="9" customFormat="1">
       <c r="A72" s="5" t="s">
         <v>53</v>
       </c>
@@ -1573,69 +1600,139 @@
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:1" s="8" customFormat="1">
+    <row r="84" spans="1:1" s="9" customFormat="1">
       <c r="A84" s="6" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="85" spans="1:1">
       <c r="A85" s="7" t="s">
-        <v>70</v>
+        <v>64</v>
       </c>
     </row>
     <row r="86" spans="1:1">
       <c r="A86" s="7" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="87" spans="1:1">
       <c r="A87" s="7" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="88" spans="1:1">
       <c r="A88" s="7" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="89" spans="1:1">
       <c r="A89" s="4" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90" s="8" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91" s="8" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92" s="8" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93" s="8" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94" s="8" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95" s="8" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="90" spans="1:1">
-      <c r="A90" t="s">
+    <row r="96" spans="1:1">
+      <c r="A96" s="8" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="91" spans="1:1">
-      <c r="A91" t="s">
+    <row r="98" spans="1:1">
+      <c r="A98" t="s">
         <v>76</v>
       </c>
     </row>
-    <row r="92" spans="1:1">
-      <c r="A92" t="s">
+    <row r="99" spans="1:1">
+      <c r="A99" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="93" spans="1:1">
-      <c r="A93" t="s">
+    <row r="100" spans="1:1">
+      <c r="A100" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="94" spans="1:1">
-      <c r="A94" t="s">
+    <row r="101" spans="1:1">
+      <c r="A101" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="95" spans="1:1">
-      <c r="A95" t="s">
+    <row r="102" spans="1:1">
+      <c r="A102" t="s">
         <v>80</v>
       </c>
     </row>
-    <row r="96" spans="1:1">
-      <c r="A96" t="s">
+    <row r="103" spans="1:1">
+      <c r="A103" t="s">
         <v>81</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111" t="s">
+        <v>89</v>
       </c>
     </row>
   </sheetData>

--- a/Verlog.xlsx
+++ b/Verlog.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="104">
   <si>
     <t/>
   </si>
@@ -249,19 +249,19 @@
     <t>v26.09.12（20260926）</t>
   </si>
   <si>
-    <t>1.镜中之战PVP改为从广场直接点入口进入（新增广场入口图片识别），不再依赖地图移动，修掉「走到一半进不去 / 卡在选择卡带界面」的问题；</t>
-  </si>
-  <si>
-    <t>2.镜中之战PVP细节加固：自动战斗按钮限制重复点击次数并补等待时间，卡带与玩法关键词识别放宽，餐厅与营业入口改为固定坐标点击，减少误点与空转；</t>
-  </si>
-  <si>
-    <t>3.奖励一键领取：活动页签由「一个大区域整体识别」拆成四个页签逐个识别并点击，漏领概率大幅降低；</t>
+    <t>1.镜中之战PVP新增广场入口图片识别</t>
+  </si>
+  <si>
+    <t>2.镜中之战PVP细节加固：自动战斗按钮限制重复点击次数并补等待时间，卡带与玩法关键词识别放宽，餐厅与营业入口改为固定坐标点击，减少误点</t>
+  </si>
+  <si>
+    <t>3.奖励一键领取：活动页签由「一个大区域整体识别」拆成四个页签逐个识别并点击</t>
   </si>
   <si>
     <t>4.奖励一键领取：去掉已失效的「活动主页」图片模板节点，改为识别活动标签后直接进入四个页签；</t>
   </si>
   <si>
-    <t>5.奖励一键领取：列表滑动检测改为「向下滑 / 向上滑」双向轮询（原来只向下滑且滑完就放弃），并去掉会导致任务报错中断的错误分支，长列表也能翻到位；</t>
+    <t>5.奖励一键领取：列表滑动检测改为「向下滑 / 向上滑」双向轮询</t>
   </si>
   <si>
     <t>6.日常收菜：每日与广场奖励节点限制重复命中次数，并去掉末尾的兜底重启节点，避免在识别不到时原地打转；</t>
@@ -286,6 +286,48 @@
   </si>
   <si>
     <t>13.README 与注意事项文档同步更新：常见问题扩充到 Q13，并明确「分辨率只能用固定档位（1280×720 / 1600×900 / 1920×1080 / 2560×1440 / 3840×2160），不要用鼠标拖窗口边框改大小」。</t>
+  </si>
+  <si>
+    <t>v26.09.13（20260928）</t>
+  </si>
+  <si>
+    <t>1.奖励一键领取：活动页签不再靠四个固定区域逐个猜，改为直接检测红点感叹号并点击对应页签，漏领与误点都更少；</t>
+  </si>
+  <si>
+    <t>2.奖励一键领取：修掉上一版遗留的「四个页签点满次数后任务直接报错中断」的问题，改为红点节点统一计次（上限 12 次）；</t>
+  </si>
+  <si>
+    <t>3.奖励一键领取：红点模板补上绿色遮罩参数，修掉「屏幕上明明有红点却识别不到、滑到超时就报错」的问题；</t>
+  </si>
+  <si>
+    <t>4.奖励一键领取：列表上下滑动各限 3 次并精简多余分支；「全部领取/全部解锁」放宽为「全部/领取/解锁」，通行证改为「赛季通行证」「角色通行证」整词识别，OCR 只认出半截也能点到；</t>
+  </si>
+  <si>
+    <t>5.魔兽追踪者（含回归赛季）：新增「活动 AP 不足」弹窗的识别与关闭，AP 用完不再卡在快速战斗界面，自动退回活动主页；</t>
+  </si>
+  <si>
+    <t>6.魔兽追踪者：进入战斗前的按钮改为连点两次并延长等待，去掉重复次数限制，修掉「点一次没反应就直接结束任务」的问题；</t>
+  </si>
+  <si>
+    <t>7.赛季活动商店、资源吸收次轮：一批点击点位的偏移补齐了负宽高，修掉「点击区域被算成 0 或 1 像素 → 取不到点击位置 → 任务报错」的红叉（次轮资源吸收切卡带时最常见）；</t>
+  </si>
+  <si>
+    <t>8.日常收菜：广场奖励识别超时由 15 秒缩短到 12 秒，并新增「结束广场流程」兜底，认不出来就跳过广场继续后面的步骤，不再原地打转；</t>
+  </si>
+  <si>
+    <t>9.免费抽抽乐：抽完后先点「确认」再点跳过，跳过按钮改为右上角固定坐标点击，避免动画没播完就点到错位置；</t>
+  </si>
+  <si>
+    <t>10.启动与图像设置：去掉「技能/过场/动画」的文字识别等待，改为直接滑动两次；「使用快捷键」改为整词识别，减少因文字没认全而卡在启动流程。</t>
+  </si>
+  <si>
+    <t>11.启动器：更新时的文件覆盖不再「写失败也当成功」（以前复制失败会被静默跳过，症状是弹窗说更新完成、实际只装了一半或版本号没变）；</t>
+  </si>
+  <si>
+    <t>12.启动器：旧版遗留清理新增「按版本号一次性清理」，本版会把 v26.09.11 留下的五个空壳管线文件从软件目录里删掉（里面已无任何节点，留着只会让人困惑）；</t>
+  </si>
+  <si>
+    <t>13.狩猎场：修掉「快速狩猎」被文字识别误认成别的字、导致进不去快速狩猎界面并原地打转的问题（识别词放宽为「快速狩」三字起匹配）。</t>
   </si>
 </sst>
 </file>
@@ -948,7 +990,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -972,9 +1014,6 @@
     </xf>
     <xf numFmtId="300" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="300" fontId="3" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1284,7 +1323,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr/>
-  <dimension ref="A111"/>
+  <dimension ref="A127"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="171.125" customWidth="1"/>
@@ -1525,7 +1564,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="65" spans="1:1" s="9" customFormat="1">
+    <row r="65" spans="1:1" s="8" customFormat="1">
       <c r="A65" s="5" t="s">
         <v>48</v>
       </c>
@@ -1550,7 +1589,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="72" spans="1:1" s="9" customFormat="1">
+    <row r="72" spans="1:1" s="8" customFormat="1">
       <c r="A72" s="5" t="s">
         <v>53</v>
       </c>
@@ -1600,7 +1639,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:1" s="9" customFormat="1">
+    <row r="84" spans="1:1" s="8" customFormat="1">
       <c r="A84" s="6" t="s">
         <v>63</v>
       </c>
@@ -1631,108 +1670,178 @@
       </c>
     </row>
     <row r="90" spans="1:1">
-      <c r="A90" s="8" t="s">
+      <c r="A90" s="4" t="s">
         <v>69</v>
       </c>
     </row>
     <row r="91" spans="1:1">
-      <c r="A91" s="8" t="s">
+      <c r="A91" s="4" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="92" spans="1:1">
-      <c r="A92" s="8" t="s">
+      <c r="A92" s="4" t="s">
         <v>71</v>
       </c>
     </row>
     <row r="93" spans="1:1">
-      <c r="A93" s="8" t="s">
+      <c r="A93" s="4" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="94" spans="1:1">
-      <c r="A94" s="8" t="s">
+      <c r="A94" s="4" t="s">
         <v>73</v>
       </c>
     </row>
     <row r="95" spans="1:1">
-      <c r="A95" s="8" t="s">
+      <c r="A95" s="4" t="s">
         <v>74</v>
       </c>
     </row>
     <row r="96" spans="1:1">
-      <c r="A96" s="8" t="s">
+      <c r="A96" s="4" t="s">
         <v>75</v>
       </c>
     </row>
     <row r="98" spans="1:1">
-      <c r="A98" t="s">
+      <c r="A98" s="4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="99" spans="1:1">
-      <c r="A99" t="s">
+      <c r="A99" s="4" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="100" spans="1:1">
-      <c r="A100" t="s">
+      <c r="A100" s="4" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="101" spans="1:1">
-      <c r="A101" t="s">
+      <c r="A101" s="4" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="102" spans="1:1">
-      <c r="A102" t="s">
+      <c r="A102" s="4" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="103" spans="1:1">
-      <c r="A103" t="s">
+      <c r="A103" s="4" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="104" spans="1:1">
-      <c r="A104" t="s">
+      <c r="A104" s="4" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="105" spans="1:1">
-      <c r="A105" t="s">
+      <c r="A105" s="4" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="106" spans="1:1">
-      <c r="A106" t="s">
+      <c r="A106" s="4" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="107" spans="1:1">
-      <c r="A107" t="s">
+      <c r="A107" s="4" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="108" spans="1:1">
-      <c r="A108" t="s">
+      <c r="A108" s="4" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="109" spans="1:1">
-      <c r="A109" t="s">
+      <c r="A109" s="4" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="110" spans="1:1">
-      <c r="A110" t="s">
+      <c r="A110" s="4" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="111" spans="1:1">
-      <c r="A111" t="s">
+      <c r="A111" s="4" t="s">
         <v>89</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113" s="4" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114" s="4" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115" s="4" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116" s="4" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118" s="4" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119" s="4" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120" s="4" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121" s="4" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123" s="4" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127" t="s">
+        <v>103</v>
       </c>
     </row>
   </sheetData>
